--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/WISCONSIN_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/WISCONSIN_2012.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C61">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C131">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C521">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C615">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C657">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C762">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C926">
